--- a/csv/articulos.xlsx
+++ b/csv/articulos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">codigo</t>
   </si>
@@ -37,46 +37,50 @@
     <t xml:space="preserve">fecha_venc</t>
   </si>
   <si>
-    <t xml:space="preserve">A001</t>
+    <t xml:space="preserve">001</t>
   </si>
   <si>
     <t xml:space="preserve">Paracetamol 500mg</t>
   </si>
   <si>
-    <t xml:space="preserve">A002</t>
+    <t xml:space="preserve">002</t>
   </si>
   <si>
     <t xml:space="preserve">Ibuprofeno 400mg</t>
   </si>
   <si>
-    <t xml:space="preserve">A003</t>
+    <t xml:space="preserve">003</t>
   </si>
   <si>
     <t xml:space="preserve">Amoxicilina 500mg</t>
   </si>
   <si>
-    <t xml:space="preserve">A004</t>
+    <t xml:space="preserve">004</t>
   </si>
   <si>
     <t xml:space="preserve">Vitamina C 1g</t>
   </si>
   <si>
-    <t xml:space="preserve">A005</t>
+    <t xml:space="preserve">005</t>
   </si>
   <si>
     <t xml:space="preserve">Alcohol 70% 500ml</t>
   </si>
   <si>
-    <t xml:space="preserve">Pan Felipe</t>
+    <t xml:space="preserve">006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novalgina 200mg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -143,8 +147,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -152,7 +160,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -283,26 +291,26 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="6.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="9.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="10.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -310,16 +318,16 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>12000</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>46032</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>46762</v>
       </c>
     </row>
@@ -327,16 +335,16 @@
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>15000</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>46058</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>46788</v>
       </c>
     </row>
@@ -344,16 +352,16 @@
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>23000</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>46093</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>46824</v>
       </c>
     </row>
@@ -361,16 +369,16 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>9000</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>46042</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>46752</v>
       </c>
     </row>
@@ -378,34 +386,34 @@
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>18000</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>46006</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>46736</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>46007</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>46737</v>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46371</v>
       </c>
     </row>
   </sheetData>
